--- a/Data/EC/NIT-9009332234.xlsx
+++ b/Data/EC/NIT-9009332234.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFE7543D-7129-48A6-A38C-E055BE678C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2081B173-E05B-4F55-ABD7-AD68E928BD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{ADA976CC-D7E4-471D-B250-D0F121D8C962}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CA94220A-BDE3-49A1-BBB2-A261A553A47B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,148 +71,148 @@
     <t>RAFAEL DIONISIO VELEZ SAN JUAN</t>
   </si>
   <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
     <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -256,7 +256,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,9 +311,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -326,7 +324,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -526,23 +526,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -570,10 +570,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -611,22 +611,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>391675</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>154425</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B76F4A2-FB0F-4791-6393-023C7D6F769A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F31D14C9-006F-DD72-2947-F8902549059C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -648,7 +648,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="645675" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -977,23 +977,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8204F79B-4EB8-45EB-AF4F-DFFD2A652C7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B7DC3B-D2EF-4F11-8B02-E0CD9E833984}">
   <dimension ref="B2:J69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="16.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1006,7 +1006,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1017,7 +1017,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1028,7 +1028,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1039,8 +1039,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1"/>
-    <row r="7" spans="2:10">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>60</v>
       </c>
@@ -1055,8 +1055,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1"/>
-    <row r="9" spans="2:10">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1071,8 +1071,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1"/>
-    <row r="11" spans="2:10">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>61</v>
       </c>
@@ -1087,8 +1087,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1"/>
-    <row r="13" spans="2:10">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>62</v>
       </c>
@@ -1107,7 +1107,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>26500</v>
+        <v>29812</v>
       </c>
       <c r="G16" s="18">
         <v>828116</v>
@@ -1159,7 +1159,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1182,7 +1182,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1205,7 +1205,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1228,7 +1228,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1251,7 +1251,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1274,7 +1274,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1297,7 +1297,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1320,7 +1320,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1343,7 +1343,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1366,7 +1366,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1389,7 +1389,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1412,7 +1412,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1435,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1458,7 +1458,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1481,7 +1481,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1504,7 +1504,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1596,7 +1596,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1619,7 +1619,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1642,7 +1642,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1665,7 +1665,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1688,7 +1688,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1711,7 +1711,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1734,7 +1734,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1757,7 +1757,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1780,7 +1780,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1803,7 +1803,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1826,7 +1826,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1849,7 +1849,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1872,7 +1872,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1895,7 +1895,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1918,7 +1918,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1941,7 +1941,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1964,7 +1964,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1987,7 +1987,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2010,7 +2010,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2033,7 +2033,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2056,7 +2056,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2079,7 +2079,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2102,7 +2102,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2125,7 +2125,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2148,7 +2148,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2171,7 +2171,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2194,7 +2194,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2217,7 +2217,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
         <v>8</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>58</v>
       </c>
       <c r="F63" s="24">
-        <v>29812</v>
+        <v>26500</v>
       </c>
       <c r="G63" s="24">
         <v>828116</v>
@@ -2240,7 +2240,7 @@
       <c r="I63" s="25"/>
       <c r="J63" s="26"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="32" t="s">
         <v>68</v>
       </c>
@@ -2251,7 +2251,7 @@
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="32" t="s">
         <v>67</v>
       </c>
